--- a/src/Excelsior.Tests/DictionarySheetTests.EnumDropdownAutoDerived.verified.xlsx
+++ b/src/Excelsior.Tests/DictionarySheetTests.EnumDropdownAutoDerived.verified.xlsx
@@ -93,7 +93,7 @@
   </sheetData>
   <autoFilter ref="A1:B3"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." sqref="B2:B3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." prompt="Select one of: Full Time, Part Time, Contract, Terminated." sqref="B2:B3">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/DictionarySheetTests.EnumDropdownAutoDerived.verified.xlsx
+++ b/src/Excelsior.Tests/DictionarySheetTests.EnumDropdownAutoDerived.verified.xlsx
@@ -93,7 +93,7 @@
   </sheetData>
   <autoFilter ref="A1:B3"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." prompt="Select one of: Full Time, Part Time, Contract, Terminated." sqref="B2:B3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." prompt="Select one of: Full Time, Part Time, Contract, Terminated" sqref="B2:B3">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/DictionarySheetTests.EnumDropdownAutoDerived.verified.xlsx
+++ b/src/Excelsior.Tests/DictionarySheetTests.EnumDropdownAutoDerived.verified.xlsx
@@ -93,7 +93,7 @@
   </sheetData>
   <autoFilter ref="A1:B3"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." sqref="B2:B3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." prompt="Select one of: Full Time, Part Time, Contract, Terminated" sqref="B2:B3">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/DictionarySheetTests.EnumDropdownAutoDerived.verified.xlsx
+++ b/src/Excelsior.Tests/DictionarySheetTests.EnumDropdownAutoDerived.verified.xlsx
@@ -101,7 +101,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Name"/>
     <column index="2" property="Status"/>
